--- a/MathTutor/questions/question.xlsx
+++ b/MathTutor/questions/question.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="75">
   <si>
     <t xml:space="preserve">question</t>
   </si>
@@ -97,6 +97,21 @@
     <t xml:space="preserve">a5:9*b1:4*</t>
   </si>
   <si>
+    <t xml:space="preserve">John has {a} apples and gets {b} more. How many apples does he have?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a5:9*b1:7*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There are {a} students in a class and {b} tables. How many students per table if evenly distributed?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a6:8*b2:4*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{a}/{b}</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ravi collected {a} stamps in his collection. If he wants to have {b} stamps in total, how many more does he need?</t>
   </si>
   <si>
@@ -115,6 +130,21 @@
     <t xml:space="preserve">a100,200,300*b50:99*</t>
   </si>
   <si>
+    <t xml:space="preserve">If you save {a} rupees  every day, how much will you have after {b} days?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a100,200,300*b10,20,30,70*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{a}*{b}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If a chocolate bar costs {a} rupees, how much would {b} cost?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a10,20,30*b3:7*</t>
+  </si>
+  <si>
     <t xml:space="preserve">Amal walked {a} kilometers in the morning and {b} kilometers in the evening. How many kilometers did he walk in total?</t>
   </si>
   <si>
@@ -136,9 +166,6 @@
     <t xml:space="preserve">a150:200*b40:50*</t>
   </si>
   <si>
-    <t xml:space="preserve">{a}*{b}</t>
-  </si>
-  <si>
     <t xml:space="preserve">{a} x {b} = </t>
   </si>
   <si>
@@ -154,9 +181,6 @@
     <t xml:space="preserve">a1:10*b1:10*</t>
   </si>
   <si>
-    <t xml:space="preserve">{a}*+b}</t>
-  </si>
-  <si>
     <t xml:space="preserve">{a} % of {b} =</t>
   </si>
   <si>
@@ -187,9 +211,6 @@
     <t xml:space="preserve">a10,20,30,40,50*b2,5,10*</t>
   </si>
   <si>
-    <t xml:space="preserve">{a}/{b}</t>
-  </si>
-  <si>
     <t xml:space="preserve">a5,10,15,20,25,30,35,40*b5*</t>
   </si>
   <si>
@@ -206,9 +227,6 @@
   </si>
   <si>
     <t xml:space="preserve">a4,5,6*b1:5*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{b}</t>
   </si>
   <si>
     <t xml:space="preserve">{a} x {b} x {c} =</t>
@@ -309,20 +327,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -338,545 +360,731 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="107.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="42.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="107.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="42.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.55"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="0" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="0" t="s">
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="0" t="s">
+      <c r="D4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="0" t="s">
+      <c r="D5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="0" t="s">
+      <c r="D6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="0" t="s">
+      <c r="D7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="F7" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="0" t="s">
+      <c r="D8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="F8" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="0" t="s">
+      <c r="D9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="B10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="D10" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="F10" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="B11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="0" t="s">
+      <c r="F12" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="0" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="0" t="n">
+      <c r="F15" s="1" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F16" s="1" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="0" t="n">
+    <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E17" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="F17" s="1" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="0" t="s">
+    <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="0" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="0" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="0" t="n">
+      <c r="F18" s="1" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E20" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="0" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="0" t="n">
+      <c r="C22" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E17" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" s="0" t="n">
+      <c r="E23" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F25" s="1" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E18" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="F18" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E19" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="F19" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="E26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="F20" s="0" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="F21" s="0" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="F22" s="0" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="E23" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="F23" s="0" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B24" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="C24" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="D24" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="F24" s="0" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="B25" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="D25" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="F25" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="B26" s="0" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="F26" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="D30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/MathTutor/questions/question.xlsx
+++ b/MathTutor/questions/question.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="68">
   <si>
     <t xml:space="preserve">question</t>
   </si>
@@ -152,9 +152,6 @@
   </si>
   <si>
     <t xml:space="preserve">a1:10*b1:10*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{a}*+b}</t>
   </si>
   <si>
     <t xml:space="preserve">{a} % of {b} =</t>
@@ -347,7 +344,7 @@
   <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="107.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="42.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.55"/>
   </cols>
@@ -646,7 +643,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="F15" s="0" t="n">
         <v>5</v>
@@ -654,19 +651,19 @@
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="C16" s="0" t="s">
         <v>46</v>
-      </c>
-      <c r="C16" s="0" t="s">
-        <v>47</v>
       </c>
       <c r="D16" s="0" t="n">
         <v>2</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F16" s="0" t="n">
         <v>5</v>
@@ -674,19 +671,19 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="0" t="s">
-        <v>46</v>
-      </c>
       <c r="C17" s="0" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D17" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F17" s="0" t="n">
         <v>10</v>
@@ -700,7 +697,7 @@
         <v>40</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D18" s="0" t="n">
         <v>2</v>
@@ -720,7 +717,7 @@
         <v>40</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D19" s="0" t="n">
         <v>3</v>
@@ -734,19 +731,19 @@
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="C20" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="D20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="0" t="s">
         <v>54</v>
-      </c>
-      <c r="D20" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="0" t="s">
-        <v>55</v>
       </c>
       <c r="F20" s="0" t="n">
         <v>5</v>
@@ -754,19 +751,19 @@
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="0" t="s">
-        <v>53</v>
-      </c>
       <c r="C21" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="0" t="s">
         <v>56</v>
-      </c>
-      <c r="D21" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="0" t="s">
-        <v>57</v>
       </c>
       <c r="F21" s="0" t="n">
         <v>5</v>
@@ -774,19 +771,19 @@
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="0" t="s">
-        <v>53</v>
-      </c>
       <c r="C22" s="0" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D22" s="0" t="n">
         <v>2</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F22" s="0" t="n">
         <v>7</v>
@@ -794,19 +791,19 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="0" t="s">
-        <v>53</v>
-      </c>
       <c r="C23" s="0" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D23" s="0" t="n">
         <v>2</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F23" s="0" t="n">
         <v>7</v>
@@ -814,19 +811,19 @@
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="C24" s="0" t="s">
+      <c r="D24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="0" t="s">
         <v>61</v>
-      </c>
-      <c r="D24" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="0" t="s">
-        <v>62</v>
       </c>
       <c r="F24" s="0" t="n">
         <v>7</v>
@@ -834,19 +831,19 @@
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B25" s="0" t="s">
         <v>40</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D25" s="0" t="n">
         <v>2</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F25" s="0" t="n">
         <v>10</v>
@@ -854,10 +851,10 @@
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" s="0" t="s">
         <v>66</v>
-      </c>
-      <c r="B26" s="0" t="s">
-        <v>67</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>43</v>
@@ -866,7 +863,7 @@
         <v>1</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F26" s="0" t="n">
         <v>10</v>
@@ -875,8 +872,8 @@
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
